--- a/bin/config/xlsx/Reward.xlsx
+++ b/bin/config/xlsx/Reward.xlsx
@@ -983,7 +983,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1124,6 +1124,40 @@
         <v>1</v>
       </c>
       <c r="E24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>7</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
         <v>2</v>
       </c>
     </row>
